--- a/Design Files/EthPoE-Module-v2.0/BOM/eSaprk_BOM_EthPoE-Module-v2.0.xlsx
+++ b/Design Files/EthPoE-Module-v2.0/BOM/eSaprk_BOM_EthPoE-Module-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="281">
   <si>
     <t>Component list</t>
   </si>
@@ -258,9 +258,6 @@
     <t>PCI Express Mini Card (Mini PCIe)</t>
   </si>
   <si>
-    <t>CONN MOD JACK 8P8C R/A SHIELDED</t>
-  </si>
-  <si>
     <t>33uH 2.3A ±20% SMD,6.6x7.3mm Inductors</t>
   </si>
   <si>
@@ -324,9 +321,6 @@
     <t>RES SMD 12.4K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>IC POE CNTRL 1 CHANNEL 8TSSOP</t>
-  </si>
-  <si>
     <t>Step-down type SOIC-8-EP DC-DC Converters ROHS</t>
   </si>
   <si>
@@ -369,9 +363,6 @@
     <t>Mini PCIE Pad</t>
   </si>
   <si>
-    <t>RJE73-188-00441</t>
-  </si>
-  <si>
     <t>SOT-723</t>
   </si>
   <si>
@@ -390,9 +381,6 @@
     <t>Res-0603</t>
   </si>
   <si>
-    <t>8-TSSOP</t>
-  </si>
-  <si>
     <t>8-SOIC-EP</t>
   </si>
   <si>
@@ -510,9 +498,6 @@
     <t>RC0603FR-0712K4L</t>
   </si>
   <si>
-    <t>TPS2375PW-1</t>
-  </si>
-  <si>
     <t>TX4138</t>
   </si>
   <si>
@@ -555,9 +540,6 @@
     <t>Taiyo Yuden</t>
   </si>
   <si>
-    <t>Amphenol Commercial</t>
-  </si>
-  <si>
     <t>KOHERelec</t>
   </si>
   <si>
@@ -684,9 +666,6 @@
     <t>C137798</t>
   </si>
   <si>
-    <t>C202190</t>
-  </si>
-  <si>
     <t>C329267</t>
   </si>
   <si>
@@ -852,13 +831,37 @@
     <t>C527051</t>
   </si>
   <si>
-    <t>Digikey</t>
-  </si>
-  <si>
     <t>RC0603FR-0722RL</t>
   </si>
   <si>
     <t>C107701</t>
+  </si>
+  <si>
+    <t>CONN JACK 1PORT 100 BASE-T PCB</t>
+  </si>
+  <si>
+    <t>ARJM11D7-114-AB-EW2</t>
+  </si>
+  <si>
+    <t>Abracon</t>
+  </si>
+  <si>
+    <t>25MHZ</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>IC POE CNTRL 1 CHANNEL 8SOIC</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>TPS2375DR</t>
+  </si>
+  <si>
+    <t>C2867397</t>
   </si>
 </sst>
 </file>
@@ -1491,6 +1494,21 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1522,21 +1540,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1914,15 +1917,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="66"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1933,7 +1936,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1958,7 +1961,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1972,7 +1975,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="67"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1983,7 +1986,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1997,7 +2000,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="68"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2022,7 +2025,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="68"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2043,7 +2046,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="68"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2064,7 +2067,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="68"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2085,7 +2088,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="68"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2102,46 +2105,46 @@
         <v>63</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>253</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="R9" s="30" t="s">
         <v>259</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="K9" s="70" t="s">
+      <c r="S9" s="30" t="s">
         <v>260</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2160,22 +2163,22 @@
         <v>64</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="L10" s="37">
         <v>10</v>
@@ -2187,8 +2190,8 @@
       <c r="N10" s="37">
         <v>100</v>
       </c>
-      <c r="O10" s="71" t="s">
-        <v>270</v>
+      <c r="O10" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P10" s="38">
         <v>1.0500000000000001E-2</v>
@@ -2216,20 +2219,20 @@
         <v>65</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I11" s="51"/>
       <c r="J11" s="51" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2241,8 +2244,8 @@
       <c r="N11" s="51">
         <v>10</v>
       </c>
-      <c r="O11" s="71" t="s">
-        <v>270</v>
+      <c r="O11" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P11" s="52">
         <v>1.7399999999999999E-2</v>
@@ -2270,22 +2273,22 @@
         <v>66</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="72" t="s">
-        <v>130</v>
+        <v>107</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>126</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="L12" s="37">
         <v>3</v>
@@ -2297,8 +2300,8 @@
       <c r="N12" s="37">
         <v>50</v>
       </c>
-      <c r="O12" s="71" t="s">
-        <v>270</v>
+      <c r="O12" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P12" s="38">
         <v>1.06E-2</v>
@@ -2326,20 +2329,20 @@
         <v>67</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I13" s="51"/>
       <c r="J13" s="51" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -2351,8 +2354,8 @@
       <c r="N13" s="51">
         <v>6</v>
       </c>
-      <c r="O13" s="71" t="s">
-        <v>270</v>
+      <c r="O13" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P13" s="52">
         <v>1.1597999999999999</v>
@@ -2380,20 +2383,20 @@
         <v>68</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2405,8 +2408,8 @@
       <c r="N14" s="37">
         <v>100</v>
       </c>
-      <c r="O14" s="71" t="s">
-        <v>270</v>
+      <c r="O14" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P14" s="38">
         <v>2.5000000000000001E-3</v>
@@ -2434,22 +2437,22 @@
         <v>69</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="72" t="s">
-        <v>133</v>
+        <v>105</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>129</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="L15" s="51">
         <v>3</v>
@@ -2461,8 +2464,8 @@
       <c r="N15" s="51">
         <v>100</v>
       </c>
-      <c r="O15" s="71" t="s">
-        <v>270</v>
+      <c r="O15" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P15" s="52">
         <v>1.9E-3</v>
@@ -2490,20 +2493,20 @@
         <v>70</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="37" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -2515,8 +2518,8 @@
       <c r="N16" s="37">
         <v>6</v>
       </c>
-      <c r="O16" s="71" t="s">
-        <v>270</v>
+      <c r="O16" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P16" s="38">
         <v>0.84960000000000002</v>
@@ -2544,20 +2547,20 @@
         <v>71</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I17" s="51"/>
       <c r="J17" s="51" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2569,8 +2572,8 @@
       <c r="N17" s="51">
         <v>100</v>
       </c>
-      <c r="O17" s="71" t="s">
-        <v>270</v>
+      <c r="O17" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P17" s="52">
         <v>2.8E-3</v>
@@ -2598,20 +2601,20 @@
         <v>72</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I18" s="37"/>
       <c r="J18" s="37" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L18" s="37">
         <v>2</v>
@@ -2623,8 +2626,8 @@
       <c r="N18" s="37">
         <v>100</v>
       </c>
-      <c r="O18" s="71" t="s">
-        <v>270</v>
+      <c r="O18" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P18" s="38">
         <v>6.8999999999999999E-3</v>
@@ -2652,20 +2655,20 @@
         <v>73</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I19" s="51"/>
       <c r="J19" s="51" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -2677,8 +2680,8 @@
       <c r="N19" s="51">
         <v>10</v>
       </c>
-      <c r="O19" s="71" t="s">
-        <v>270</v>
+      <c r="O19" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P19" s="52">
         <v>4.2299999999999997E-2</v>
@@ -2706,20 +2709,20 @@
         <v>74</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I20" s="37"/>
       <c r="J20" s="37" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2731,8 +2734,8 @@
       <c r="N20" s="37">
         <v>10</v>
       </c>
-      <c r="O20" s="71" t="s">
-        <v>270</v>
+      <c r="O20" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P20" s="38">
         <v>4.6899999999999997E-2</v>
@@ -2760,20 +2763,20 @@
         <v>75</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I21" s="51"/>
       <c r="J21" s="51" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2785,8 +2788,8 @@
       <c r="N21" s="51">
         <v>10</v>
       </c>
-      <c r="O21" s="71" t="s">
-        <v>270</v>
+      <c r="O21" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P21" s="52">
         <v>4.5600000000000002E-2</v>
@@ -2814,20 +2817,20 @@
         <v>76</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="37" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2839,8 +2842,8 @@
       <c r="N22" s="37">
         <v>20</v>
       </c>
-      <c r="O22" s="71" t="s">
-        <v>270</v>
+      <c r="O22" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P22" s="38">
         <v>6.2E-2</v>
@@ -2868,20 +2871,20 @@
         <v>77</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I23" s="51"/>
       <c r="J23" s="51" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L23" s="51">
         <v>2</v>
@@ -2893,8 +2896,8 @@
       <c r="N23" s="51">
         <v>15</v>
       </c>
-      <c r="O23" s="71" t="s">
-        <v>270</v>
+      <c r="O23" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P23" s="52">
         <v>0.18790000000000001</v>
@@ -2913,50 +2916,50 @@
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>269</v>
-      </c>
-      <c r="D24" s="72" t="s">
+        <v>262</v>
+      </c>
+      <c r="D24" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="72" t="s">
+      <c r="E24" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="73" t="s">
-        <v>271</v>
-      </c>
-      <c r="G24" s="72" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="I24" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="J24" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="K24" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="L24" s="72">
+      <c r="F24" s="63" t="s">
+        <v>264</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="I24" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="J24" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="K24" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="L24" s="62">
         <v>1</v>
       </c>
-      <c r="M24" s="72">
+      <c r="M24" s="62">
         <f>L24*5</f>
         <v>5</v>
       </c>
-      <c r="N24" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="O24" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="P24" s="74" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q24" s="74" t="s">
-        <v>268</v>
+      <c r="N24" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="O24" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="P24" s="64" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q24" s="64" t="s">
+        <v>261</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -2974,25 +2977,25 @@
         <v>36</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>116</v>
+        <v>273</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>178</v>
+        <v>274</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
@@ -3004,15 +3007,15 @@
       <c r="N25" s="51">
         <v>6</v>
       </c>
-      <c r="O25" s="71" t="s">
-        <v>277</v>
+      <c r="O25" s="61" t="s">
+        <v>276</v>
       </c>
       <c r="P25" s="52">
-        <v>3.16</v>
+        <v>3.47</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="16">P25*N25</f>
-        <v>18.96</v>
+        <v>20.82</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -3030,23 +3033,23 @@
         <v>37</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I26" s="37"/>
       <c r="J26" s="37" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -3058,8 +3061,8 @@
       <c r="N26" s="37">
         <v>6</v>
       </c>
-      <c r="O26" s="71" t="s">
-        <v>270</v>
+      <c r="O26" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P26" s="38">
         <v>0.94820000000000004</v>
@@ -3084,23 +3087,23 @@
         <v>38</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I27" s="51"/>
       <c r="J27" s="51" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="K27" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -3112,8 +3115,8 @@
       <c r="N27" s="51">
         <v>20</v>
       </c>
-      <c r="O27" s="71" t="s">
-        <v>270</v>
+      <c r="O27" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P27" s="52">
         <v>3.3500000000000002E-2</v>
@@ -3138,23 +3141,23 @@
         <v>39</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I28" s="37"/>
       <c r="J28" s="37" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3166,8 +3169,8 @@
       <c r="N28" s="37">
         <v>6</v>
       </c>
-      <c r="O28" s="71" t="s">
-        <v>270</v>
+      <c r="O28" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P28" s="38">
         <v>0.3453</v>
@@ -3192,23 +3195,23 @@
         <v>40</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I29" s="51"/>
       <c r="J29" s="51" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -3220,8 +3223,8 @@
       <c r="N29" s="51">
         <v>100</v>
       </c>
-      <c r="O29" s="71" t="s">
-        <v>270</v>
+      <c r="O29" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P29" s="52">
         <v>5.9999999999999995E-4</v>
@@ -3246,25 +3249,25 @@
         <v>41</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3276,8 +3279,8 @@
       <c r="N30" s="37">
         <v>50</v>
       </c>
-      <c r="O30" s="71" t="s">
-        <v>270</v>
+      <c r="O30" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P30" s="38">
         <v>5.4999999999999997E-3</v>
@@ -3302,25 +3305,25 @@
         <v>42</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="L31" s="51">
         <v>1</v>
@@ -3332,8 +3335,8 @@
       <c r="N31" s="51">
         <v>100</v>
       </c>
-      <c r="O31" s="71" t="s">
-        <v>270</v>
+      <c r="O31" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P31" s="52">
         <v>6.9999999999999999E-4</v>
@@ -3358,25 +3361,25 @@
         <v>43</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3388,8 +3391,8 @@
       <c r="N32" s="37">
         <v>10</v>
       </c>
-      <c r="O32" s="71" t="s">
-        <v>270</v>
+      <c r="O32" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P32" s="38">
         <v>7.4800000000000005E-2</v>
@@ -3414,25 +3417,25 @@
         <v>44</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -3444,8 +3447,8 @@
       <c r="N33" s="51">
         <v>100</v>
       </c>
-      <c r="O33" s="71" t="s">
-        <v>270</v>
+      <c r="O33" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P33" s="52">
         <v>6.9999999999999999E-4</v>
@@ -3470,25 +3473,25 @@
         <v>45</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="L34" s="37">
         <v>1</v>
@@ -3500,8 +3503,8 @@
       <c r="N34" s="37">
         <v>100</v>
       </c>
-      <c r="O34" s="71" t="s">
-        <v>270</v>
+      <c r="O34" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P34" s="38">
         <v>1E-3</v>
@@ -3526,25 +3529,25 @@
         <v>46</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="G35" s="72" t="s">
-        <v>151</v>
+        <v>119</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>147</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
@@ -3556,8 +3559,8 @@
       <c r="N35" s="51">
         <v>100</v>
       </c>
-      <c r="O35" s="71" t="s">
-        <v>270</v>
+      <c r="O35" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P35" s="52">
         <v>1.1999999999999999E-3</v>
@@ -3582,25 +3585,25 @@
         <v>47</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -3612,8 +3615,8 @@
       <c r="N36" s="37">
         <v>100</v>
       </c>
-      <c r="O36" s="71" t="s">
-        <v>270</v>
+      <c r="O36" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P36" s="38">
         <v>8.9999999999999998E-4</v>
@@ -3638,25 +3641,25 @@
         <v>48</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -3668,8 +3671,8 @@
       <c r="N37" s="51">
         <v>50</v>
       </c>
-      <c r="O37" s="71" t="s">
-        <v>270</v>
+      <c r="O37" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P37" s="52">
         <v>5.4999999999999997E-3</v>
@@ -3694,25 +3697,25 @@
         <v>49</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="L38" s="37">
         <v>17</v>
@@ -3724,8 +3727,8 @@
       <c r="N38" s="37">
         <v>100</v>
       </c>
-      <c r="O38" s="71" t="s">
-        <v>270</v>
+      <c r="O38" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P38" s="38">
         <v>8.9999999999999998E-4</v>
@@ -3750,25 +3753,25 @@
         <v>50</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -3780,8 +3783,8 @@
       <c r="N39" s="51">
         <v>100</v>
       </c>
-      <c r="O39" s="71" t="s">
-        <v>270</v>
+      <c r="O39" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P39" s="52">
         <v>1E-3</v>
@@ -3806,25 +3809,25 @@
         <v>51</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="L40" s="37">
         <v>2</v>
@@ -3836,8 +3839,8 @@
       <c r="N40" s="37">
         <v>100</v>
       </c>
-      <c r="O40" s="71" t="s">
-        <v>270</v>
+      <c r="O40" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P40" s="38">
         <v>1.1000000000000001E-3</v>
@@ -3862,25 +3865,25 @@
         <v>52</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="L41" s="51">
         <v>2</v>
@@ -3892,8 +3895,8 @@
       <c r="N41" s="51">
         <v>100</v>
       </c>
-      <c r="O41" s="71" t="s">
-        <v>270</v>
+      <c r="O41" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P41" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3918,25 +3921,25 @@
         <v>53</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="L42" s="37">
         <v>4</v>
@@ -3948,8 +3951,8 @@
       <c r="N42" s="37">
         <v>100</v>
       </c>
-      <c r="O42" s="71" t="s">
-        <v>270</v>
+      <c r="O42" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P42" s="38">
         <v>1E-3</v>
@@ -3974,25 +3977,25 @@
         <v>54</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="L43" s="51">
         <v>1</v>
@@ -4004,8 +4007,8 @@
       <c r="N43" s="51">
         <v>100</v>
       </c>
-      <c r="O43" s="71" t="s">
-        <v>270</v>
+      <c r="O43" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P43" s="52">
         <v>2.7000000000000001E-3</v>
@@ -4030,25 +4033,25 @@
         <v>55</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L44" s="37">
         <v>4</v>
@@ -4060,8 +4063,8 @@
       <c r="N44" s="37">
         <v>100</v>
       </c>
-      <c r="O44" s="71" t="s">
-        <v>270</v>
+      <c r="O44" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P44" s="38">
         <v>1.1999999999999999E-3</v>
@@ -4086,25 +4089,25 @@
         <v>56</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L45" s="51">
         <v>1</v>
@@ -4116,8 +4119,8 @@
       <c r="N45" s="51">
         <v>100</v>
       </c>
-      <c r="O45" s="71" t="s">
-        <v>270</v>
+      <c r="O45" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P45" s="52">
         <v>1.2999999999999999E-3</v>
@@ -4142,25 +4145,25 @@
         <v>57</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="L46" s="37">
         <v>1</v>
@@ -4172,8 +4175,8 @@
       <c r="N46" s="37">
         <v>100</v>
       </c>
-      <c r="O46" s="71" t="s">
-        <v>270</v>
+      <c r="O46" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P46" s="38">
         <v>1.2999999999999999E-3</v>
@@ -4198,25 +4201,25 @@
         <v>58</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>101</v>
+        <v>277</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="G47" s="51" t="s">
-        <v>163</v>
+        <v>279</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I47" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
@@ -4225,14 +4228,18 @@
         <f t="shared" ref="M47" si="37">L47*5</f>
         <v>5</v>
       </c>
-      <c r="N47" s="51"/>
-      <c r="O47" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="P47" s="52"/>
+      <c r="N47" s="51">
+        <v>6</v>
+      </c>
+      <c r="O47" s="61" t="s">
+        <v>263</v>
+      </c>
+      <c r="P47" s="52">
+        <v>2.1716000000000002</v>
+      </c>
       <c r="Q47" s="52">
         <f t="shared" ref="Q47" si="38">P47*N47</f>
-        <v>0</v>
+        <v>13.029600000000002</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="59"/>
@@ -4250,23 +4257,23 @@
         <v>59</v>
       </c>
       <c r="E48" s="37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I48" s="37"/>
       <c r="J48" s="37" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="K48" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L48" s="37">
         <v>1</v>
@@ -4278,8 +4285,8 @@
       <c r="N48" s="37">
         <v>6</v>
       </c>
-      <c r="O48" s="71" t="s">
-        <v>270</v>
+      <c r="O48" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P48" s="38">
         <v>0.64910000000000001</v>
@@ -4304,23 +4311,23 @@
         <v>60</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G49" s="51" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I49" s="51"/>
       <c r="J49" s="51" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L49" s="51">
         <v>1</v>
@@ -4332,8 +4339,8 @@
       <c r="N49" s="51">
         <v>6</v>
       </c>
-      <c r="O49" s="71" t="s">
-        <v>270</v>
+      <c r="O49" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P49" s="52">
         <v>2.6839</v>
@@ -4358,23 +4365,23 @@
         <v>61</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I50" s="37"/>
       <c r="J50" s="37" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="L50" s="37">
         <v>1</v>
@@ -4386,8 +4393,8 @@
       <c r="N50" s="37">
         <v>6</v>
       </c>
-      <c r="O50" s="71" t="s">
-        <v>270</v>
+      <c r="O50" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P50" s="38">
         <v>0.56479999999999997</v>
@@ -4412,23 +4419,23 @@
         <v>62</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I51" s="51"/>
       <c r="J51" s="51" t="s">
-        <v>225</v>
-      </c>
-      <c r="K51" s="37" t="s">
-        <v>268</v>
+        <v>218</v>
+      </c>
+      <c r="K51" s="51" t="s">
+        <v>275</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -4440,8 +4447,8 @@
       <c r="N51" s="51">
         <v>6</v>
       </c>
-      <c r="O51" s="71" t="s">
-        <v>270</v>
+      <c r="O51" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="P51" s="52">
         <v>0.25240000000000001</v>
@@ -4467,17 +4474,17 @@
       <c r="K52" s="45"/>
       <c r="L52" s="45"/>
       <c r="M52" s="45"/>
-      <c r="N52" s="68" t="s">
+      <c r="N52" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="69"/>
-      <c r="P52" s="69"/>
+      <c r="O52" s="74"/>
+      <c r="P52" s="74"/>
       <c r="Q52" s="48">
         <f>SUM(Q10:Q51)</f>
-        <v>75.907100000000014</v>
-      </c>
-      <c r="R52" s="64"/>
-      <c r="S52" s="65"/>
+        <v>90.796700000000016</v>
+      </c>
+      <c r="R52" s="69"/>
+      <c r="S52" s="70"/>
     </row>
     <row r="53" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -4493,17 +4500,17 @@
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
       <c r="M53" s="10"/>
-      <c r="N53" s="68" t="s">
+      <c r="N53" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="O53" s="69"/>
-      <c r="P53" s="69"/>
+      <c r="O53" s="74"/>
+      <c r="P53" s="74"/>
       <c r="Q53" s="49">
         <f>Q52/5</f>
-        <v>15.181420000000003</v>
-      </c>
-      <c r="R53" s="66"/>
-      <c r="S53" s="67"/>
+        <v>18.159340000000004</v>
+      </c>
+      <c r="R53" s="71"/>
+      <c r="S53" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4552,11 +4559,12 @@
     <hyperlink ref="O51" r:id="rId36"/>
     <hyperlink ref="O12" r:id="rId37"/>
     <hyperlink ref="O15" r:id="rId38"/>
-    <hyperlink ref="O25" r:id="rId39"/>
-    <hyperlink ref="O35" r:id="rId40"/>
+    <hyperlink ref="O35" r:id="rId39"/>
+    <hyperlink ref="O25" r:id="rId40"/>
+    <hyperlink ref="O47" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
-  <drawing r:id="rId42"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
+  <drawing r:id="rId43"/>
 </worksheet>
 </file>
--- a/Design Files/EthPoE-Module-v2.0/BOM/eSaprk_BOM_EthPoE-Module-v2.0.xlsx
+++ b/Design Files/EthPoE-Module-v2.0/BOM/eSaprk_BOM_EthPoE-Module-v2.0.xlsx
@@ -168,18 +168,12 @@
     <t>R9</t>
   </si>
   <si>
-    <t>R10, R11, R12, R14, R23, R25, R29, R30, R31, R34, R35, R36, R37, R38, R39, R41, R42</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
     <t>R15, R16</t>
   </si>
   <si>
-    <t>R17, R33</t>
-  </si>
-  <si>
     <t>R18, R19, R27, R28</t>
   </si>
   <si>
@@ -862,6 +856,12 @@
   </si>
   <si>
     <t>C2867397</t>
+  </si>
+  <si>
+    <t>R10, R14, R23, R25, R29, R30, R31, R34, R35, R36, R37, R38, R39</t>
+  </si>
+  <si>
+    <t>R12, R17, R33</t>
   </si>
 </sst>
 </file>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2102,49 +2102,49 @@
         <v>20</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>251</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="K9" s="60" t="s">
+      <c r="N9" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>258</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2160,25 +2160,25 @@
         <v>21</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L10" s="37">
         <v>10</v>
@@ -2191,7 +2191,7 @@
         <v>100</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P10" s="38">
         <v>1.0500000000000001E-2</v>
@@ -2216,23 +2216,23 @@
         <v>22</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I11" s="51"/>
       <c r="J11" s="51" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2245,7 +2245,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P11" s="52">
         <v>1.7399999999999999E-2</v>
@@ -2270,25 +2270,25 @@
         <v>23</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L12" s="37">
         <v>3</v>
@@ -2301,7 +2301,7 @@
         <v>50</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P12" s="38">
         <v>1.06E-2</v>
@@ -2326,23 +2326,23 @@
         <v>24</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I13" s="51"/>
       <c r="J13" s="51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         <v>6</v>
       </c>
       <c r="O13" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P13" s="52">
         <v>1.1597999999999999</v>
@@ -2380,23 +2380,23 @@
         <v>25</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2409,7 +2409,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P14" s="38">
         <v>2.5000000000000001E-3</v>
@@ -2434,25 +2434,25 @@
         <v>26</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G15" s="62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L15" s="51">
         <v>3</v>
@@ -2465,7 +2465,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P15" s="52">
         <v>1.9E-3</v>
@@ -2490,23 +2490,23 @@
         <v>27</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="37" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         <v>6</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P16" s="38">
         <v>0.84960000000000002</v>
@@ -2544,23 +2544,23 @@
         <v>28</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I17" s="51"/>
       <c r="J17" s="51" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2573,7 +2573,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P17" s="52">
         <v>2.8E-3</v>
@@ -2598,23 +2598,23 @@
         <v>29</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I18" s="37"/>
       <c r="J18" s="37" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L18" s="37">
         <v>2</v>
@@ -2627,7 +2627,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P18" s="38">
         <v>6.8999999999999999E-3</v>
@@ -2652,23 +2652,23 @@
         <v>30</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I19" s="51"/>
       <c r="J19" s="51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -2681,7 +2681,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P19" s="52">
         <v>4.2299999999999997E-2</v>
@@ -2706,23 +2706,23 @@
         <v>31</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I20" s="37"/>
       <c r="J20" s="37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2735,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P20" s="38">
         <v>4.6899999999999997E-2</v>
@@ -2760,23 +2760,23 @@
         <v>32</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I21" s="51"/>
       <c r="J21" s="51" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2789,7 +2789,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P21" s="52">
         <v>4.5600000000000002E-2</v>
@@ -2814,23 +2814,23 @@
         <v>33</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="37" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>20</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P22" s="38">
         <v>6.2E-2</v>
@@ -2868,23 +2868,23 @@
         <v>34</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I23" s="51"/>
       <c r="J23" s="51" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L23" s="51">
         <v>2</v>
@@ -2897,7 +2897,7 @@
         <v>15</v>
       </c>
       <c r="O23" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P23" s="52">
         <v>0.18790000000000001</v>
@@ -2916,31 +2916,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D24" s="62" t="s">
         <v>35</v>
       </c>
       <c r="E24" s="62" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F24" s="63" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I24" s="62" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J24" s="62" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K24" s="62" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L24" s="62">
         <v>1</v>
@@ -2950,16 +2950,16 @@
         <v>5</v>
       </c>
       <c r="N24" s="62" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="O24" s="62" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P24" s="64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q24" s="64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -2977,25 +2977,25 @@
         <v>36</v>
       </c>
       <c r="E25" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="H25" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="F25" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>273</v>
-      </c>
-      <c r="H25" s="51" t="s">
-        <v>274</v>
-      </c>
       <c r="I25" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
@@ -3008,7 +3008,7 @@
         <v>6</v>
       </c>
       <c r="O25" s="61" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P25" s="52">
         <v>3.47</v>
@@ -3033,23 +3033,23 @@
         <v>37</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I26" s="37"/>
       <c r="J26" s="37" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -3062,7 +3062,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P26" s="38">
         <v>0.94820000000000004</v>
@@ -3087,23 +3087,23 @@
         <v>38</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I27" s="51"/>
       <c r="J27" s="51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K27" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -3116,7 +3116,7 @@
         <v>20</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P27" s="52">
         <v>3.3500000000000002E-2</v>
@@ -3141,23 +3141,23 @@
         <v>39</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I28" s="37"/>
       <c r="J28" s="37" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3170,7 +3170,7 @@
         <v>6</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P28" s="38">
         <v>0.3453</v>
@@ -3195,23 +3195,23 @@
         <v>40</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I29" s="51"/>
       <c r="J29" s="51" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -3224,7 +3224,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P29" s="52">
         <v>5.9999999999999995E-4</v>
@@ -3249,25 +3249,25 @@
         <v>41</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3280,7 +3280,7 @@
         <v>50</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P30" s="38">
         <v>5.4999999999999997E-3</v>
@@ -3305,25 +3305,25 @@
         <v>42</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L31" s="51">
         <v>1</v>
@@ -3336,7 +3336,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P31" s="52">
         <v>6.9999999999999999E-4</v>
@@ -3361,25 +3361,25 @@
         <v>43</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3392,7 +3392,7 @@
         <v>10</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P32" s="38">
         <v>7.4800000000000005E-2</v>
@@ -3417,25 +3417,25 @@
         <v>44</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -3448,7 +3448,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P33" s="52">
         <v>6.9999999999999999E-4</v>
@@ -3473,25 +3473,25 @@
         <v>45</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L34" s="37">
         <v>1</v>
@@ -3504,7 +3504,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P34" s="38">
         <v>1E-3</v>
@@ -3529,25 +3529,25 @@
         <v>46</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G35" s="62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
@@ -3560,7 +3560,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P35" s="52">
         <v>1.1999999999999999E-3</v>
@@ -3585,25 +3585,25 @@
         <v>47</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -3616,7 +3616,7 @@
         <v>100</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P36" s="38">
         <v>8.9999999999999998E-4</v>
@@ -3641,25 +3641,25 @@
         <v>48</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -3672,7 +3672,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P37" s="52">
         <v>5.4999999999999997E-3</v>
@@ -3684,7 +3684,7 @@
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="46">
         <f>ROW(B38) - ROW($B$9)</f>
@@ -3694,41 +3694,41 @@
         <v>16</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>49</v>
+        <v>279</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L38" s="37">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M38" s="37">
         <f>L38*5</f>
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="N38" s="37">
         <v>100</v>
       </c>
       <c r="O38" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P38" s="38">
         <v>8.9999999999999998E-4</v>
@@ -3750,28 +3750,28 @@
         <v>16</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -3784,7 +3784,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P39" s="52">
         <v>1E-3</v>
@@ -3806,28 +3806,28 @@
         <v>16</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L40" s="37">
         <v>2</v>
@@ -3840,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P40" s="38">
         <v>1.1000000000000001E-3</v>
@@ -3862,41 +3862,41 @@
         <v>16</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>52</v>
+        <v>280</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L41" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M41" s="51">
         <f t="shared" ref="M41" si="31">L41*5</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N41" s="51">
         <v>100</v>
       </c>
       <c r="O41" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P41" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3918,28 +3918,28 @@
         <v>16</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L42" s="37">
         <v>4</v>
@@ -3952,7 +3952,7 @@
         <v>100</v>
       </c>
       <c r="O42" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P42" s="38">
         <v>1E-3</v>
@@ -3974,28 +3974,28 @@
         <v>16</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L43" s="51">
         <v>1</v>
@@ -4008,7 +4008,7 @@
         <v>100</v>
       </c>
       <c r="O43" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P43" s="52">
         <v>2.7000000000000001E-3</v>
@@ -4030,28 +4030,28 @@
         <v>16</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L44" s="37">
         <v>4</v>
@@ -4064,7 +4064,7 @@
         <v>100</v>
       </c>
       <c r="O44" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P44" s="38">
         <v>1.1999999999999999E-3</v>
@@ -4086,28 +4086,28 @@
         <v>16</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L45" s="51">
         <v>1</v>
@@ -4120,7 +4120,7 @@
         <v>100</v>
       </c>
       <c r="O45" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P45" s="52">
         <v>1.2999999999999999E-3</v>
@@ -4142,28 +4142,28 @@
         <v>16</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L46" s="37">
         <v>1</v>
@@ -4176,7 +4176,7 @@
         <v>100</v>
       </c>
       <c r="O46" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P46" s="38">
         <v>1.2999999999999999E-3</v>
@@ -4198,28 +4198,28 @@
         <v>17</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E47" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="F47" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="G47" s="51" t="s">
         <v>277</v>
       </c>
-      <c r="F47" s="51" t="s">
+      <c r="H47" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="I47" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="J47" s="51" t="s">
         <v>278</v>
       </c>
-      <c r="G47" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="H47" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="I47" s="51" t="s">
-        <v>261</v>
-      </c>
-      <c r="J47" s="51" t="s">
-        <v>280</v>
-      </c>
       <c r="K47" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
@@ -4232,7 +4232,7 @@
         <v>6</v>
       </c>
       <c r="O47" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P47" s="52">
         <v>2.1716000000000002</v>
@@ -4254,26 +4254,26 @@
         <v>17</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E48" s="37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I48" s="37"/>
       <c r="J48" s="37" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K48" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L48" s="37">
         <v>1</v>
@@ -4286,7 +4286,7 @@
         <v>6</v>
       </c>
       <c r="O48" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P48" s="38">
         <v>0.64910000000000001</v>
@@ -4308,26 +4308,26 @@
         <v>17</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G49" s="51" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I49" s="51"/>
       <c r="J49" s="51" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L49" s="51">
         <v>1</v>
@@ -4340,7 +4340,7 @@
         <v>6</v>
       </c>
       <c r="O49" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P49" s="52">
         <v>2.6839</v>
@@ -4362,26 +4362,26 @@
         <v>18</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I50" s="37"/>
       <c r="J50" s="37" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L50" s="37">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="O50" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P50" s="38">
         <v>0.56479999999999997</v>
@@ -4416,26 +4416,26 @@
         <v>19</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I51" s="51"/>
       <c r="J51" s="51" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -4448,7 +4448,7 @@
         <v>6</v>
       </c>
       <c r="O51" s="61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P51" s="52">
         <v>0.25240000000000001</v>
